--- a/Kappa_scoring/Gold_Standard_Overview_23022026.xlsx
+++ b/Kappa_scoring/Gold_Standard_Overview_23022026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sem.l.kampman/Documents/1_phd_projecten/1_umcu/1_active_projects/6_quips_llm/GitHub/quips/quips_private/Kappa_scoring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16384AD9-5A98-8944-AF59-87BAC3D46588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC6636F-B959-584C-81F2-150803F3A61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4E3F4CC3-0563-A146-9958-FFCF367891F9}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16380" xr2:uid="{4E3F4CC3-0563-A146-9958-FFCF367891F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="325">
   <si>
     <t>Study_ID</t>
   </si>
@@ -473,9 +473,6 @@
     <t>Verboom</t>
   </si>
   <si>
-    <t>Amantini_2025</t>
-  </si>
-  <si>
     <t>Cleri_2023</t>
   </si>
   <si>
@@ -1097,10 +1094,16 @@
     <t>Pires</t>
   </si>
   <si>
-    <t>Deb_2001</t>
-  </si>
-  <si>
     <t>Gallucci</t>
+  </si>
+  <si>
+    <t>author_year</t>
+  </si>
+  <si>
+    <t>Deb_1998</t>
+  </si>
+  <si>
+    <t>Amantini_2005</t>
   </si>
 </sst>
 </file>
@@ -1172,16 +1175,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1550,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="D1" t="s">
         <v>102</v>
@@ -1590,22 +1592,22 @@
       <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2542,10 +2544,10 @@
         <v>0</v>
       </c>
       <c r="C32" t="s">
+        <v>240</v>
+      </c>
+      <c r="D32" t="s">
         <v>241</v>
-      </c>
-      <c r="D32" t="s">
-        <v>242</v>
       </c>
       <c r="E32" t="s">
         <v>2</v>
@@ -2574,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E33" t="s">
         <v>3</v>
@@ -2606,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="C34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E34" t="s">
         <v>2</v>
@@ -2638,10 +2640,10 @@
         <v>0</v>
       </c>
       <c r="C35" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D35" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E35" t="s">
         <v>2</v>
@@ -2670,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="C36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E36" t="s">
         <v>2</v>
@@ -2702,10 +2704,10 @@
         <v>0</v>
       </c>
       <c r="C37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E37" t="s">
         <v>2</v>
@@ -2734,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="C38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E38" t="s">
         <v>2</v>
@@ -2766,10 +2768,10 @@
         <v>0</v>
       </c>
       <c r="C39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E39" t="s">
         <v>6</v>
@@ -2798,10 +2800,10 @@
         <v>0</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E40" t="s">
         <v>2</v>
@@ -2830,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E41" t="s">
         <v>2</v>
@@ -2862,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E42" t="s">
         <v>2</v>
@@ -2894,22 +2896,22 @@
         <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D43" t="s">
+        <v>241</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" t="s">
+        <v>2</v>
+      </c>
+      <c r="H43" t="s">
         <v>242</v>
-      </c>
-      <c r="E43" t="s">
-        <v>2</v>
-      </c>
-      <c r="F43" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" t="s">
-        <v>2</v>
-      </c>
-      <c r="H43" t="s">
-        <v>243</v>
       </c>
       <c r="I43" t="s">
         <v>6</v>
@@ -2926,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E44" t="s">
         <v>2</v>
@@ -2958,10 +2960,10 @@
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E45" t="s">
         <v>2</v>
@@ -2990,10 +2992,10 @@
         <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D46" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E46" t="s">
         <v>6</v>
@@ -3022,10 +3024,10 @@
         <v>0</v>
       </c>
       <c r="C47" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E47" t="s">
         <v>2</v>
@@ -3054,10 +3056,10 @@
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D48" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E48" t="s">
         <v>2</v>
@@ -3086,10 +3088,10 @@
         <v>0</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D49" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E49" t="s">
         <v>2</v>
@@ -3118,10 +3120,10 @@
         <v>0</v>
       </c>
       <c r="C50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D50" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E50" t="s">
         <v>2</v>
@@ -3150,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="C51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D51" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E51" t="s">
         <v>2</v>
@@ -3182,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D52" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E52" t="s">
         <v>2</v>
@@ -3214,10 +3216,10 @@
         <v>0</v>
       </c>
       <c r="C53" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D53" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E53" t="s">
         <v>3</v>
@@ -3246,10 +3248,10 @@
         <v>0</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D54" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E54" t="s">
         <v>2</v>
@@ -3278,10 +3280,10 @@
         <v>0</v>
       </c>
       <c r="C55" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E55" t="s">
         <v>2</v>
@@ -3310,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="C56" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E56" t="s">
         <v>2</v>
@@ -3342,10 +3344,10 @@
         <v>0</v>
       </c>
       <c r="C57" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D57" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E57" t="s">
         <v>2</v>
@@ -3374,10 +3376,10 @@
         <v>0</v>
       </c>
       <c r="C58" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D58" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E58" t="s">
         <v>2</v>
@@ -3406,10 +3408,10 @@
         <v>0</v>
       </c>
       <c r="C59" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E59" t="s">
         <v>6</v>
@@ -3438,10 +3440,10 @@
         <v>0</v>
       </c>
       <c r="C60" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E60" t="s">
         <v>2</v>
@@ -3470,10 +3472,10 @@
         <v>0</v>
       </c>
       <c r="C61" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E61" t="s">
         <v>2</v>
@@ -3502,10 +3504,10 @@
         <v>0</v>
       </c>
       <c r="C62" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E62" t="s">
         <v>3</v>
@@ -3534,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="C63" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E63" t="s">
         <v>3</v>
@@ -3566,10 +3568,10 @@
         <v>0</v>
       </c>
       <c r="C64" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E64" t="s">
         <v>6</v>
@@ -3598,10 +3600,10 @@
         <v>0</v>
       </c>
       <c r="C65" t="s">
+        <v>160</v>
+      </c>
+      <c r="D65" t="s">
         <v>161</v>
-      </c>
-      <c r="D65" t="s">
-        <v>162</v>
       </c>
       <c r="E65" t="s">
         <v>2</v>
@@ -3630,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="C66" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E66" t="s">
         <v>2</v>
@@ -3662,10 +3664,10 @@
         <v>0</v>
       </c>
       <c r="C67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E67" t="s">
         <v>2</v>
@@ -3694,10 +3696,10 @@
         <v>0</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E68" t="s">
         <v>2</v>
@@ -3726,10 +3728,10 @@
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E69" t="s">
         <v>2</v>
@@ -3758,10 +3760,10 @@
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D70" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E70" t="s">
         <v>3</v>
@@ -3790,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="C71" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D71" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E71" t="s">
         <v>3</v>
@@ -3822,10 +3824,10 @@
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E72" t="s">
         <v>2</v>
@@ -4654,10 +4656,10 @@
         <v>0</v>
       </c>
       <c r="C98" t="s">
+        <v>222</v>
+      </c>
+      <c r="D98" t="s">
         <v>223</v>
-      </c>
-      <c r="D98" t="s">
-        <v>224</v>
       </c>
       <c r="E98" t="s">
         <v>6</v>
@@ -4686,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="C99" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E99" t="s">
         <v>3</v>
@@ -4718,10 +4720,10 @@
         <v>0</v>
       </c>
       <c r="C100" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E100" t="s">
         <v>2</v>
@@ -4750,10 +4752,10 @@
         <v>0</v>
       </c>
       <c r="C101" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E101" t="s">
         <v>2</v>
@@ -4782,10 +4784,10 @@
         <v>0</v>
       </c>
       <c r="C102" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E102" t="s">
         <v>2</v>
@@ -4814,10 +4816,10 @@
         <v>0</v>
       </c>
       <c r="C103" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E103" t="s">
         <v>2</v>
@@ -4846,10 +4848,10 @@
         <v>0</v>
       </c>
       <c r="C104" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E104" t="s">
         <v>3</v>
@@ -4878,10 +4880,10 @@
         <v>0</v>
       </c>
       <c r="C105" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E105" t="s">
         <v>6</v>
@@ -4910,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="C106" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E106" t="s">
         <v>2</v>
@@ -4942,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="C107" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E107" t="s">
         <v>3</v>
@@ -4974,10 +4976,10 @@
         <v>0</v>
       </c>
       <c r="C108" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E108" t="s">
         <v>2</v>
@@ -5006,10 +5008,10 @@
         <v>0</v>
       </c>
       <c r="C109" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E109" t="s">
         <v>2</v>
@@ -5038,10 +5040,10 @@
         <v>0</v>
       </c>
       <c r="C110" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E110" t="s">
         <v>6</v>
@@ -5070,10 +5072,10 @@
         <v>0</v>
       </c>
       <c r="C111" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E111" t="s">
         <v>2</v>
@@ -5102,10 +5104,10 @@
         <v>0</v>
       </c>
       <c r="C112" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E112" t="s">
         <v>2</v>
@@ -5134,10 +5136,10 @@
         <v>0</v>
       </c>
       <c r="C113" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E113" t="s">
         <v>6</v>
@@ -5166,10 +5168,10 @@
         <v>0</v>
       </c>
       <c r="C114" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E114" t="s">
         <v>2</v>
@@ -5198,10 +5200,10 @@
         <v>0</v>
       </c>
       <c r="C115" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E115" t="s">
         <v>6</v>
@@ -5230,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="C116" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E116" t="s">
         <v>2</v>
@@ -5262,10 +5264,10 @@
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E117" t="s">
         <v>2</v>
@@ -5294,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="C118" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E118" t="s">
         <v>6</v>
@@ -5326,10 +5328,10 @@
         <v>0</v>
       </c>
       <c r="C119" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E119" t="s">
         <v>6</v>
@@ -5358,10 +5360,10 @@
         <v>0</v>
       </c>
       <c r="C120" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D120" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E120" t="s">
         <v>6</v>
@@ -5390,10 +5392,10 @@
         <v>0</v>
       </c>
       <c r="C121" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D121" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E121" t="s">
         <v>6</v>
@@ -5422,10 +5424,10 @@
         <v>0</v>
       </c>
       <c r="C122" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D122" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E122" t="s">
         <v>2</v>
@@ -5454,10 +5456,10 @@
         <v>0</v>
       </c>
       <c r="C123" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D123" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E123" t="s">
         <v>6</v>
@@ -5486,10 +5488,10 @@
         <v>0</v>
       </c>
       <c r="C124" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D124" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E124" t="s">
         <v>3</v>
@@ -5518,10 +5520,10 @@
         <v>0</v>
       </c>
       <c r="C125" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D125" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E125" t="s">
         <v>3</v>
@@ -5550,10 +5552,10 @@
         <v>0</v>
       </c>
       <c r="C126" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D126" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E126" t="s">
         <v>6</v>
@@ -5582,10 +5584,10 @@
         <v>0</v>
       </c>
       <c r="C127" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D127" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E127" t="s">
         <v>6</v>
@@ -5614,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="C128" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D128" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E128" t="s">
         <v>2</v>
@@ -5646,10 +5648,10 @@
         <v>0</v>
       </c>
       <c r="C129" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D129" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E129" t="s">
         <v>2</v>
@@ -5678,10 +5680,10 @@
         <v>0</v>
       </c>
       <c r="C130" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D130" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E130" t="s">
         <v>2</v>
@@ -5710,10 +5712,10 @@
         <v>0</v>
       </c>
       <c r="C131" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D131" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E131" t="s">
         <v>2</v>
@@ -5742,10 +5744,10 @@
         <v>0</v>
       </c>
       <c r="C132" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D132" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E132" t="s">
         <v>3</v>
@@ -5774,10 +5776,10 @@
         <v>0</v>
       </c>
       <c r="C133" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D133" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E133" t="s">
         <v>6</v>
@@ -5806,10 +5808,10 @@
         <v>0</v>
       </c>
       <c r="C134" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D134" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E134" t="s">
         <v>6</v>
@@ -5838,10 +5840,10 @@
         <v>0</v>
       </c>
       <c r="C135" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D135" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E135" t="s">
         <v>3</v>
@@ -5870,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="C136" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D136" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E136" t="s">
         <v>2</v>
@@ -5902,10 +5904,10 @@
         <v>0</v>
       </c>
       <c r="C137" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D137" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E137" t="s">
         <v>6</v>
@@ -5934,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="C138" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D138" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E138" t="s">
         <v>2</v>
@@ -5966,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="C139" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D139" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E139" t="s">
         <v>3</v>
@@ -5998,10 +6000,10 @@
         <v>0</v>
       </c>
       <c r="C140" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D140" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E140" t="s">
         <v>2</v>
@@ -6030,10 +6032,10 @@
         <v>0</v>
       </c>
       <c r="C141" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D141" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E141" t="s">
         <v>3</v>
@@ -6062,28 +6064,28 @@
         <v>0</v>
       </c>
       <c r="C142" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D142" t="s">
+        <v>223</v>
+      </c>
+      <c r="E142" t="s">
+        <v>2</v>
+      </c>
+      <c r="F142" t="s">
+        <v>3</v>
+      </c>
+      <c r="G142" t="s">
+        <v>2</v>
+      </c>
+      <c r="H142" t="s">
+        <v>3</v>
+      </c>
+      <c r="I142" t="s">
+        <v>6</v>
+      </c>
+      <c r="J142" t="s">
         <v>224</v>
-      </c>
-      <c r="E142" t="s">
-        <v>2</v>
-      </c>
-      <c r="F142" t="s">
-        <v>3</v>
-      </c>
-      <c r="G142" t="s">
-        <v>2</v>
-      </c>
-      <c r="H142" t="s">
-        <v>3</v>
-      </c>
-      <c r="I142" t="s">
-        <v>6</v>
-      </c>
-      <c r="J142" t="s">
-        <v>225</v>
       </c>
       <c r="K142" t="s">
         <v>3</v>
@@ -6094,10 +6096,10 @@
         <v>0</v>
       </c>
       <c r="C143" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D143" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E143" t="s">
         <v>3</v>
@@ -6126,10 +6128,10 @@
         <v>0</v>
       </c>
       <c r="C144" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D144" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E144" t="s">
         <v>2</v>
@@ -6158,10 +6160,10 @@
         <v>0</v>
       </c>
       <c r="C145" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D145" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E145" t="s">
         <v>2</v>
@@ -6190,10 +6192,10 @@
         <v>0</v>
       </c>
       <c r="C146" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D146" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E146" t="s">
         <v>2</v>
@@ -6222,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="C147" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D147" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E147" t="s">
         <v>2</v>
@@ -6254,10 +6256,10 @@
         <v>0</v>
       </c>
       <c r="C148" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E148" t="s">
         <v>3</v>
@@ -6286,10 +6288,10 @@
         <v>0</v>
       </c>
       <c r="C149" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D149" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E149" t="s">
         <v>6</v>
@@ -6318,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="C150" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D150" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E150" t="s">
         <v>2</v>
@@ -6350,10 +6352,10 @@
         <v>0</v>
       </c>
       <c r="C151" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D151" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E151" t="s">
         <v>2</v>
@@ -6382,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="C152" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D152" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E152" t="s">
         <v>2</v>
@@ -6414,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="C153" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D153" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E153" t="s">
         <v>2</v>
@@ -6446,10 +6448,10 @@
         <v>0</v>
       </c>
       <c r="C154" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D154" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E154" t="s">
         <v>3</v>
@@ -6478,10 +6480,10 @@
         <v>0</v>
       </c>
       <c r="C155" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D155" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E155" t="s">
         <v>6</v>
@@ -6510,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="C156" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D156" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E156" t="s">
         <v>6</v>
@@ -6542,10 +6544,10 @@
         <v>0</v>
       </c>
       <c r="C157" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D157" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E157" t="s">
         <v>2</v>
@@ -6574,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="C158" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D158" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E158" t="s">
         <v>2</v>
@@ -6606,10 +6608,10 @@
         <v>0</v>
       </c>
       <c r="C159" t="s">
+        <v>319</v>
+      </c>
+      <c r="D159" t="s">
         <v>320</v>
-      </c>
-      <c r="D159" t="s">
-        <v>321</v>
       </c>
       <c r="E159" t="s">
         <v>2</v>
@@ -6638,10 +6640,10 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D160" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E160" t="s">
         <v>2</v>
@@ -6670,10 +6672,10 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D161" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E161" t="s">
         <v>6</v>
@@ -6702,10 +6704,10 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D162" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E162" t="s">
         <v>2</v>
@@ -6734,10 +6736,10 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D163" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E163" t="s">
         <v>6</v>
@@ -6766,10 +6768,10 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D164" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E164" t="s">
         <v>6</v>
@@ -6798,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D165" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E165" t="s">
         <v>6</v>
@@ -6830,10 +6832,10 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D166" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E166" t="s">
         <v>3</v>
@@ -6862,10 +6864,10 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D167" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E167" t="s">
         <v>6</v>
@@ -6894,10 +6896,10 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D168" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E168" t="s">
         <v>2</v>
@@ -6926,10 +6928,10 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D169" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E169" t="s">
         <v>3</v>
@@ -6958,10 +6960,10 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D170" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E170" t="s">
         <v>3</v>
@@ -6990,10 +6992,10 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E171" t="s">
         <v>3</v>
@@ -7022,10 +7024,10 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D172" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E172" t="s">
         <v>6</v>
@@ -7054,10 +7056,10 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D173" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E173" t="s">
         <v>6</v>
@@ -7086,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D174" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E174" t="s">
         <v>2</v>
@@ -7118,10 +7120,10 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D175" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E175" t="s">
         <v>2</v>
@@ -7150,10 +7152,10 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D176" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E176" t="s">
         <v>2</v>
@@ -7182,10 +7184,10 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D177" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E177" t="s">
         <v>3</v>
@@ -7214,10 +7216,10 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D178" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E178" t="s">
         <v>2</v>
@@ -7246,10 +7248,10 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D179" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E179" t="s">
         <v>6</v>
@@ -7273,15 +7275,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D180" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E180" t="s">
         <v>6</v>
@@ -7310,10 +7312,10 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D181" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E181" t="s">
         <v>6</v>
@@ -7342,10 +7344,10 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E182" t="s">
         <v>2</v>
@@ -7374,10 +7376,10 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D183" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E183" t="s">
         <v>2</v>
@@ -7406,10 +7408,10 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D184" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E184" t="s">
         <v>6</v>
@@ -7438,10 +7440,10 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E185" t="s">
         <v>2</v>
@@ -7470,10 +7472,10 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D186" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E186" t="s">
         <v>3</v>
@@ -7502,10 +7504,10 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D187" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E187" t="s">
         <v>2</v>
@@ -7534,10 +7536,10 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
+        <v>283</v>
+      </c>
+      <c r="D188" t="s">
         <v>284</v>
-      </c>
-      <c r="D188" t="s">
-        <v>285</v>
       </c>
       <c r="E188" t="s">
         <v>3</v>
@@ -7566,10 +7568,10 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D189" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E189" t="s">
         <v>6</v>
@@ -7598,10 +7600,10 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D190" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E190" t="s">
         <v>2</v>
@@ -7630,10 +7632,10 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D191" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E191" t="s">
         <v>6</v>
@@ -7662,10 +7664,10 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D192" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E192" t="s">
         <v>3</v>
@@ -7694,10 +7696,10 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D193" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E193" t="s">
         <v>6</v>
@@ -7726,10 +7728,10 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D194" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E194" t="s">
         <v>6</v>
@@ -7758,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D195" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E195" t="s">
         <v>2</v>
@@ -7790,10 +7792,10 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D196" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E196" t="s">
         <v>6</v>
@@ -7822,10 +7824,10 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D197" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E197" t="s">
         <v>3</v>
@@ -7854,10 +7856,10 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D198" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E198" t="s">
         <v>6</v>
@@ -7886,10 +7888,10 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D199" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E199" t="s">
         <v>2</v>
@@ -7918,10 +7920,10 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D200" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E200" t="s">
         <v>2</v>
@@ -7950,10 +7952,10 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D201" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E201" t="s">
         <v>2</v>
@@ -7982,10 +7984,10 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D202" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E202" t="s">
         <v>3</v>
@@ -8014,10 +8016,10 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D203" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E203" t="s">
         <v>3</v>
@@ -8046,10 +8048,10 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D204" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E204" t="s">
         <v>2</v>
@@ -8078,10 +8080,10 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D205" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E205" t="s">
         <v>6</v>
@@ -8110,10 +8112,10 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D206" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E206" t="s">
         <v>2</v>
@@ -8143,10 +8145,10 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D207" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E207" t="s">
         <v>2</v>
@@ -8175,10 +8177,10 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E208" t="s">
         <v>6</v>
@@ -8207,10 +8209,10 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D209" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E209" t="s">
         <v>6</v>
@@ -8239,10 +8241,10 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D210" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E210" t="s">
         <v>6</v>
@@ -8271,10 +8273,10 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D211" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E211" t="s">
         <v>3</v>
@@ -8303,10 +8305,10 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E212" t="s">
         <v>3</v>
@@ -8335,10 +8337,10 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D213" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E213" t="s">
         <v>2</v>
@@ -8367,10 +8369,10 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D214" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E214" t="s">
         <v>6</v>
@@ -8399,10 +8401,10 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D215" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E215" t="s">
         <v>2</v>
@@ -8431,10 +8433,10 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
+        <v>308</v>
+      </c>
+      <c r="D216" t="s">
         <v>309</v>
-      </c>
-      <c r="D216" t="s">
-        <v>310</v>
       </c>
       <c r="E216" t="s">
         <v>2</v>
@@ -8463,10 +8465,10 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D217" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E217" t="s">
         <v>2</v>
@@ -8495,10 +8497,10 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D218" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E218" t="s">
         <v>2</v>
@@ -8527,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D219" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E219" t="s">
         <v>2</v>
@@ -8559,10 +8561,10 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D220" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E220" t="s">
         <v>2</v>
@@ -8591,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D221" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E221" t="s">
         <v>2</v>
@@ -8623,10 +8625,10 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D222" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E222" t="s">
         <v>2</v>
@@ -8655,10 +8657,10 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D223" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E223" t="s">
         <v>2</v>
@@ -8687,10 +8689,10 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D224" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E224" t="s">
         <v>2</v>
@@ -8719,10 +8721,10 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D225" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E225" t="s">
         <v>2</v>
@@ -8751,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D226" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E226" t="s">
         <v>3</v>
@@ -8783,10 +8785,10 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D227" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E227" t="s">
         <v>6</v>
@@ -8815,10 +8817,10 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D228" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E228" t="s">
         <v>6</v>
@@ -8847,10 +8849,10 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D229" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E229" t="s">
         <v>3</v>
@@ -8879,10 +8881,10 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D230" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E230" t="s">
         <v>2</v>
@@ -8911,10 +8913,10 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D231" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E231" t="s">
         <v>2</v>
@@ -8943,10 +8945,10 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D232" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E232" t="s">
         <v>2</v>
@@ -8975,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D233" t="s">
         <v>113</v>
@@ -9007,7 +9009,7 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D234" t="s">
         <v>113</v>
@@ -9039,7 +9041,7 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D235" t="s">
         <v>113</v>
@@ -9071,7 +9073,7 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D236" t="s">
         <v>113</v>
@@ -9103,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D237" t="s">
         <v>113</v>
@@ -9135,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D238" t="s">
         <v>113</v>
@@ -9167,7 +9169,7 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D239" t="s">
         <v>113</v>
@@ -9199,7 +9201,7 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D240" t="s">
         <v>113</v>
@@ -9231,7 +9233,7 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D241" t="s">
         <v>113</v>
@@ -9263,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D242" t="s">
         <v>113</v>
@@ -9295,7 +9297,7 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D243" t="s">
         <v>113</v>
@@ -9327,7 +9329,7 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D244" t="s">
         <v>113</v>
@@ -9359,7 +9361,7 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D245" t="s">
         <v>113</v>
@@ -9391,7 +9393,7 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D246" t="s">
         <v>113</v>
@@ -9423,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D247" t="s">
         <v>113</v>
@@ -9455,7 +9457,7 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D248" t="s">
         <v>113</v>
@@ -9487,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D249" t="s">
         <v>113</v>
@@ -9519,7 +9521,7 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D250" t="s">
         <v>113</v>
@@ -9551,7 +9553,7 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D251" t="s">
         <v>113</v>
@@ -9583,7 +9585,7 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D252" t="s">
         <v>113</v>
@@ -9615,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D253" t="s">
         <v>113</v>
@@ -9647,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
-        <v>114</v>
+        <v>324</v>
       </c>
       <c r="D254" t="s">
         <v>113</v>
@@ -10927,10 +10929,10 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
+        <v>290</v>
+      </c>
+      <c r="D294" t="s">
         <v>291</v>
-      </c>
-      <c r="D294" t="s">
-        <v>292</v>
       </c>
       <c r="E294" t="s">
         <v>2</v>
@@ -10959,10 +10961,10 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D295" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E295" t="s">
         <v>3</v>
@@ -10991,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D296" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E296" t="s">
         <v>3</v>
@@ -11023,10 +11025,10 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D297" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E297" t="s">
         <v>6</v>
@@ -11055,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D298" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E298" t="s">
         <v>6</v>
@@ -11087,10 +11089,10 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D299" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E299" t="s">
         <v>2</v>
